--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,112 +421,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CÓDIGO_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NOMBRE_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SECTOR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MUNICIPIO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CÓDIGO_SNIES_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>NOMBRE_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>NÚMERO_PERIODOS_DE_DURACIÓN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PERIODICIDAD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>COSTO_MATRÍCULA_ESTUD_NUEVOS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PERIODICIDAD_ADMISIONES</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FECHA_DE_REGISTRO_EN_SNIES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_AMPLIO</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_DETALLADO</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PROGINSTI</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>FECHA_OBTENCION</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>DIVISIÓN UNINORTE</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -598,7 +586,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>42240</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -698,7 +686,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>42435</v>
       </c>
       <c r="O3" t="inlineStr">
@@ -798,7 +786,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -896,7 +884,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -994,7 +982,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>42435</v>
       </c>
       <c r="O6" t="inlineStr">
@@ -1094,7 +1082,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -1194,7 +1182,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -1294,7 +1282,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O9" t="inlineStr">
@@ -1394,7 +1382,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O10" t="inlineStr">
@@ -1494,7 +1482,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O11" t="inlineStr">
@@ -1594,7 +1582,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" s="1" t="n">
         <v>36110</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -1694,7 +1682,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" s="1" t="n">
         <v>36108</v>
       </c>
       <c r="O13" t="inlineStr">
@@ -1792,7 +1780,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -1892,7 +1880,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" s="1" t="n">
         <v>38119</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -1992,7 +1980,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" s="1" t="n">
         <v>39484</v>
       </c>
       <c r="O16" t="inlineStr">
@@ -2092,7 +2080,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="N17" s="1" t="n">
         <v>39688</v>
       </c>
       <c r="O17" t="inlineStr">
@@ -2192,7 +2180,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="N18" s="1" t="n">
         <v>39459</v>
       </c>
       <c r="O18" t="inlineStr">
@@ -2292,7 +2280,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="N19" s="1" t="n">
         <v>39840</v>
       </c>
       <c r="O19" t="inlineStr">
@@ -2392,7 +2380,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N20" s="1" t="n">
         <v>41774</v>
       </c>
       <c r="O20" t="inlineStr">
@@ -2492,7 +2480,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="N21" s="1" t="n">
         <v>42680</v>
       </c>
       <c r="O21" t="inlineStr">
@@ -2592,7 +2580,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="N22" s="1" t="n">
         <v>37139</v>
       </c>
       <c r="O22" t="inlineStr">
@@ -2692,7 +2680,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="N23" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O23" t="inlineStr">
@@ -2790,7 +2778,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="N24" s="1" t="n">
         <v>42413</v>
       </c>
       <c r="O24" t="inlineStr">
@@ -2888,7 +2876,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="N25" s="1" t="n">
         <v>42404</v>
       </c>
       <c r="O25" t="inlineStr">
@@ -2988,7 +2976,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="N26" s="1" t="n">
         <v>37508</v>
       </c>
       <c r="O26" t="inlineStr">
@@ -3088,7 +3076,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="N27" s="1" t="n">
         <v>37237</v>
       </c>
       <c r="O27" t="inlineStr">
@@ -3188,7 +3176,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="N28" s="1" t="n">
         <v>40052</v>
       </c>
       <c r="O28" t="inlineStr">
@@ -3288,7 +3276,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="N29" s="1" t="n">
         <v>43848</v>
       </c>
       <c r="O29" t="inlineStr">
@@ -3388,7 +3376,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="N30" s="1" t="n">
         <v>42492</v>
       </c>
       <c r="O30" t="inlineStr">
@@ -3486,7 +3474,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N31" s="2" t="n">
+      <c r="N31" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O31" t="inlineStr">
@@ -3586,7 +3574,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="N32" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O32" t="inlineStr">
@@ -3686,7 +3674,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N33" s="2" t="n">
+      <c r="N33" s="1" t="n">
         <v>42633</v>
       </c>
       <c r="O33" t="inlineStr">
@@ -3784,7 +3772,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="N34" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="O34" t="inlineStr">
@@ -3882,7 +3870,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="N35" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="O35" t="inlineStr">
@@ -3982,7 +3970,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="N36" s="1" t="n">
         <v>44216</v>
       </c>
       <c r="O36" t="inlineStr">
@@ -4082,7 +4070,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="N37" s="1" t="n">
         <v>37725</v>
       </c>
       <c r="O37" t="inlineStr">
@@ -4182,7 +4170,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="N38" s="1" t="n">
         <v>42811</v>
       </c>
       <c r="O38" t="inlineStr">
@@ -4280,7 +4268,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="N39" s="1" t="n">
         <v>43854</v>
       </c>
       <c r="O39" t="inlineStr">
@@ -4380,7 +4368,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="N40" s="1" t="n">
         <v>41106</v>
       </c>
       <c r="O40" t="inlineStr">
@@ -4480,7 +4468,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="N41" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O41" t="inlineStr">
@@ -4580,7 +4568,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N42" s="2" t="n">
+      <c r="N42" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O42" t="inlineStr">
@@ -4678,7 +4666,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N43" s="2" t="n">
+      <c r="N43" s="1" t="n">
         <v>36562</v>
       </c>
       <c r="O43" t="inlineStr">
@@ -4776,7 +4764,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N44" s="2" t="n">
+      <c r="N44" s="1" t="n">
         <v>41670</v>
       </c>
       <c r="O44" t="inlineStr">
@@ -4874,7 +4862,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N45" s="2" t="n">
+      <c r="N45" s="1" t="n">
         <v>39778</v>
       </c>
       <c r="O45" t="inlineStr">
@@ -4974,7 +4962,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N46" s="2" t="n">
+      <c r="N46" s="1" t="n">
         <v>42926</v>
       </c>
       <c r="O46" t="inlineStr">
@@ -5072,7 +5060,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N47" s="2" t="n">
+      <c r="N47" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="O47" t="inlineStr">
@@ -5172,7 +5160,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N48" s="2" t="n">
+      <c r="N48" s="1" t="n">
         <v>37215</v>
       </c>
       <c r="O48" t="inlineStr">
@@ -5270,7 +5258,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N49" s="2" t="n">
+      <c r="N49" s="1" t="n">
         <v>42484</v>
       </c>
       <c r="O49" t="inlineStr">
@@ -5368,7 +5356,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N50" s="2" t="n">
+      <c r="N50" s="1" t="n">
         <v>42408</v>
       </c>
       <c r="O50" t="inlineStr">
@@ -5466,7 +5454,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N51" s="2" t="n">
+      <c r="N51" s="1" t="n">
         <v>42408</v>
       </c>
       <c r="O51" t="inlineStr">
@@ -5564,7 +5552,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N52" s="2" t="n">
+      <c r="N52" s="1" t="n">
         <v>42408</v>
       </c>
       <c r="O52" t="inlineStr">
@@ -5664,7 +5652,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N53" s="2" t="n">
+      <c r="N53" s="1" t="n">
         <v>41897</v>
       </c>
       <c r="O53" t="inlineStr">
@@ -5764,7 +5752,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N54" s="2" t="n">
+      <c r="N54" s="1" t="n">
         <v>42260</v>
       </c>
       <c r="O54" t="inlineStr">
@@ -5862,7 +5850,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N55" s="2" t="n">
+      <c r="N55" s="1" t="n">
         <v>37217</v>
       </c>
       <c r="O55" t="inlineStr">
@@ -5960,7 +5948,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N56" s="2" t="n">
+      <c r="N56" s="1" t="n">
         <v>41172</v>
       </c>
       <c r="O56" t="inlineStr">
@@ -6060,7 +6048,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N57" s="2" t="n">
+      <c r="N57" s="1" t="n">
         <v>39174</v>
       </c>
       <c r="O57" t="inlineStr">
@@ -6160,7 +6148,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N58" s="2" t="n">
+      <c r="N58" s="1" t="n">
         <v>40843</v>
       </c>
       <c r="O58" t="inlineStr">
@@ -6260,7 +6248,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N59" s="2" t="n">
+      <c r="N59" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="O59" t="inlineStr">
@@ -6360,7 +6348,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N60" s="2" t="n">
+      <c r="N60" s="1" t="n">
         <v>43011</v>
       </c>
       <c r="O60" t="inlineStr">
@@ -6458,7 +6446,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N61" s="2" t="n">
+      <c r="N61" s="1" t="n">
         <v>38835</v>
       </c>
       <c r="O61" t="inlineStr">
@@ -6556,7 +6544,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N62" s="2" t="n">
+      <c r="N62" s="1" t="n">
         <v>41600</v>
       </c>
       <c r="O62" t="inlineStr">
@@ -6656,7 +6644,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N63" s="2" t="n">
+      <c r="N63" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="O63" t="inlineStr">
@@ -6756,7 +6744,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N64" s="2" t="n">
+      <c r="N64" s="1" t="n">
         <v>45117</v>
       </c>
       <c r="O64" t="inlineStr">
@@ -6856,7 +6844,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N65" s="2" t="n">
+      <c r="N65" s="1" t="n">
         <v>45155</v>
       </c>
       <c r="O65" t="inlineStr">
@@ -6956,7 +6944,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N66" s="2" t="n">
+      <c r="N66" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="O66" t="inlineStr">
@@ -7056,7 +7044,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N67" s="2" t="n">
+      <c r="N67" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O67" t="inlineStr">
@@ -7156,7 +7144,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N68" s="2" t="n">
+      <c r="N68" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="O68" t="inlineStr">
@@ -7254,7 +7242,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N69" s="2" t="n">
+      <c r="N69" s="1" t="n">
         <v>42138</v>
       </c>
       <c r="O69" t="inlineStr">
@@ -7354,7 +7342,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N70" s="2" t="n">
+      <c r="N70" s="1" t="n">
         <v>45133</v>
       </c>
       <c r="O70" t="inlineStr">
@@ -7454,7 +7442,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N71" s="2" t="n">
+      <c r="N71" s="1" t="n">
         <v>39483</v>
       </c>
       <c r="O71" t="inlineStr">
@@ -7554,7 +7542,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N72" s="2" t="n">
+      <c r="N72" s="1" t="n">
         <v>42838</v>
       </c>
       <c r="O72" t="inlineStr">
@@ -7654,7 +7642,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N73" s="2" t="n">
+      <c r="N73" s="1" t="n">
         <v>41938</v>
       </c>
       <c r="O73" t="inlineStr">
@@ -7754,7 +7742,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N74" s="2" t="n">
+      <c r="N74" s="1" t="n">
         <v>39401</v>
       </c>
       <c r="O74" t="inlineStr">
@@ -7854,7 +7842,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N75" s="2" t="n">
+      <c r="N75" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O75" t="inlineStr">
@@ -7954,7 +7942,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N76" s="2" t="n">
+      <c r="N76" s="1" t="n">
         <v>43016</v>
       </c>
       <c r="O76" t="inlineStr">
@@ -8054,7 +8042,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N77" s="2" t="n">
+      <c r="N77" s="1" t="n">
         <v>42152</v>
       </c>
       <c r="O77" t="inlineStr">
@@ -8152,7 +8140,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N78" s="2" t="n">
+      <c r="N78" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O78" t="inlineStr">
@@ -8250,7 +8238,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N79" s="2" t="n">
+      <c r="N79" s="1" t="n">
         <v>42466</v>
       </c>
       <c r="O79" t="inlineStr">
@@ -8348,7 +8336,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N80" s="2" t="n">
+      <c r="N80" s="1" t="n">
         <v>40764</v>
       </c>
       <c r="O80" t="inlineStr">
@@ -8446,7 +8434,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N81" s="2" t="n">
+      <c r="N81" s="1" t="n">
         <v>36746</v>
       </c>
       <c r="O81" t="inlineStr">
@@ -8546,7 +8534,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N82" s="2" t="n">
+      <c r="N82" s="1" t="n">
         <v>42984</v>
       </c>
       <c r="O82" t="inlineStr">
@@ -8646,7 +8634,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N83" s="2" t="n">
+      <c r="N83" s="1" t="n">
         <v>42418</v>
       </c>
       <c r="O83" t="inlineStr">
@@ -8746,7 +8734,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N84" s="2" t="n">
+      <c r="N84" s="1" t="n">
         <v>41296</v>
       </c>
       <c r="O84" t="inlineStr">
@@ -8846,7 +8834,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N85" s="2" t="n">
+      <c r="N85" s="1" t="n">
         <v>42670</v>
       </c>
       <c r="O85" t="inlineStr">
@@ -8946,7 +8934,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N86" s="2" t="n">
+      <c r="N86" s="1" t="n">
         <v>42609</v>
       </c>
       <c r="O86" t="inlineStr">
@@ -9044,7 +9032,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N87" s="2" t="n">
+      <c r="N87" s="1" t="n">
         <v>44403</v>
       </c>
       <c r="O87" t="inlineStr">
@@ -9144,7 +9132,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N88" s="2" t="n">
+      <c r="N88" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O88" t="inlineStr">
@@ -9244,7 +9232,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N89" s="2" t="n">
+      <c r="N89" s="1" t="n">
         <v>39653</v>
       </c>
       <c r="O89" t="inlineStr">
@@ -9342,7 +9330,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N90" s="2" t="n">
+      <c r="N90" s="1" t="n">
         <v>41599</v>
       </c>
       <c r="O90" t="inlineStr">
@@ -9442,7 +9430,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N91" s="2" t="n">
+      <c r="N91" s="1" t="n">
         <v>42019</v>
       </c>
       <c r="O91" t="inlineStr">
@@ -9542,7 +9530,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N92" s="2" t="n">
+      <c r="N92" s="1" t="n">
         <v>41847</v>
       </c>
       <c r="O92" t="inlineStr">
@@ -9642,7 +9630,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N93" s="2" t="n">
+      <c r="N93" s="1" t="n">
         <v>41442</v>
       </c>
       <c r="O93" t="inlineStr">
@@ -9740,7 +9728,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N94" s="2" t="n">
+      <c r="N94" s="1" t="n">
         <v>41809</v>
       </c>
       <c r="O94" t="inlineStr">
@@ -9838,7 +9826,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N95" s="2" t="n">
+      <c r="N95" s="1" t="n">
         <v>37138</v>
       </c>
       <c r="O95" t="inlineStr">
@@ -9938,7 +9926,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N96" s="2" t="n">
+      <c r="N96" s="1" t="n">
         <v>40921</v>
       </c>
       <c r="O96" t="inlineStr">
@@ -10038,7 +10026,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N97" s="2" t="n">
+      <c r="N97" s="1" t="n">
         <v>42152</v>
       </c>
       <c r="O97" t="inlineStr">
@@ -10138,7 +10126,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N98" s="2" t="n">
+      <c r="N98" s="1" t="n">
         <v>42848</v>
       </c>
       <c r="O98" t="inlineStr">
@@ -10238,7 +10226,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N99" s="2" t="n">
+      <c r="N99" s="1" t="n">
         <v>42138</v>
       </c>
       <c r="O99" t="inlineStr">
@@ -10336,7 +10324,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N100" s="2" t="n">
+      <c r="N100" s="1" t="n">
         <v>42609</v>
       </c>
       <c r="O100" t="inlineStr">
@@ -10434,7 +10422,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N101" s="2" t="n">
+      <c r="N101" s="1" t="n">
         <v>42571</v>
       </c>
       <c r="O101" t="inlineStr">
@@ -10534,7 +10522,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N102" s="2" t="n">
+      <c r="N102" s="1" t="n">
         <v>41831</v>
       </c>
       <c r="O102" t="inlineStr">
@@ -10632,7 +10620,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N103" s="2" t="n">
+      <c r="N103" s="1" t="n">
         <v>41232</v>
       </c>
       <c r="O103" t="inlineStr">
@@ -10730,7 +10718,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N104" s="2" t="n">
+      <c r="N104" s="1" t="n">
         <v>43483</v>
       </c>
       <c r="O104" t="inlineStr">
@@ -10830,7 +10818,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N105" s="2" t="n">
+      <c r="N105" s="1" t="n">
         <v>42290</v>
       </c>
       <c r="O105" t="inlineStr">
@@ -10930,7 +10918,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N106" s="2" t="n">
+      <c r="N106" s="1" t="n">
         <v>41806</v>
       </c>
       <c r="O106" t="inlineStr">
@@ -11028,7 +11016,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N107" s="2" t="n">
+      <c r="N107" s="1" t="n">
         <v>37568</v>
       </c>
       <c r="O107" t="inlineStr">
@@ -11128,7 +11116,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N108" s="2" t="n">
+      <c r="N108" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O108" t="inlineStr">
@@ -11224,7 +11212,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N109" s="2" t="n">
+      <c r="N109" s="1" t="n">
         <v>38681</v>
       </c>
       <c r="O109" t="inlineStr">
@@ -11324,7 +11312,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N110" s="2" t="n">
+      <c r="N110" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="O110" t="inlineStr">
@@ -11422,7 +11410,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N111" s="2" t="n">
+      <c r="N111" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O111" t="inlineStr">
@@ -11522,7 +11510,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N112" s="2" t="n">
+      <c r="N112" s="1" t="n">
         <v>42762</v>
       </c>
       <c r="O112" t="inlineStr">
@@ -11622,7 +11610,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N113" s="2" t="n">
+      <c r="N113" s="1" t="n">
         <v>42571</v>
       </c>
       <c r="O113" t="inlineStr">
@@ -11720,7 +11708,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N114" s="2" t="n">
+      <c r="N114" s="1" t="n">
         <v>42952</v>
       </c>
       <c r="O114" t="inlineStr">
@@ -11820,7 +11808,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N115" s="2" t="n">
+      <c r="N115" s="1" t="n">
         <v>44368</v>
       </c>
       <c r="O115" t="inlineStr">
@@ -11920,7 +11908,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N116" s="2" t="n">
+      <c r="N116" s="1" t="n">
         <v>42818</v>
       </c>
       <c r="O116" t="inlineStr">
@@ -12020,7 +12008,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N117" s="2" t="n">
+      <c r="N117" s="1" t="n">
         <v>45208</v>
       </c>
       <c r="O117" t="inlineStr">
@@ -12118,7 +12106,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N118" s="2" t="n">
+      <c r="N118" s="1" t="n">
         <v>44146</v>
       </c>
       <c r="O118" t="inlineStr">
@@ -12218,7 +12206,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N119" s="2" t="n">
+      <c r="N119" s="1" t="n">
         <v>44146</v>
       </c>
       <c r="O119" t="inlineStr">
@@ -12318,7 +12306,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N120" s="2" t="n">
+      <c r="N120" s="1" t="n">
         <v>44146</v>
       </c>
       <c r="O120" t="inlineStr">
@@ -12418,7 +12406,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N121" s="2" t="n">
+      <c r="N121" s="1" t="n">
         <v>40280</v>
       </c>
       <c r="O121" t="inlineStr">
@@ -12518,7 +12506,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N122" s="2" t="n">
+      <c r="N122" s="1" t="n">
         <v>45355</v>
       </c>
       <c r="O122" t="inlineStr">
@@ -12616,7 +12604,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N123" s="2" t="n">
+      <c r="N123" s="1" t="n">
         <v>41282</v>
       </c>
       <c r="O123" t="inlineStr">
@@ -12716,7 +12704,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N124" s="2" t="n">
+      <c r="N124" s="1" t="n">
         <v>41283</v>
       </c>
       <c r="O124" t="inlineStr">
@@ -12814,7 +12802,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N125" s="2" t="n">
+      <c r="N125" s="1" t="n">
         <v>43340</v>
       </c>
       <c r="O125" t="inlineStr">
@@ -12912,7 +12900,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N126" s="2" t="n">
+      <c r="N126" s="1" t="n">
         <v>42452</v>
       </c>
       <c r="O126" t="inlineStr">
@@ -13010,7 +12998,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N127" s="2" t="n">
+      <c r="N127" s="1" t="n">
         <v>42967</v>
       </c>
       <c r="O127" t="inlineStr">
@@ -13108,7 +13096,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N128" s="2" t="n">
+      <c r="N128" s="1" t="n">
         <v>42967</v>
       </c>
       <c r="O128" t="inlineStr">
@@ -13206,7 +13194,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N129" s="2" t="n">
+      <c r="N129" s="1" t="n">
         <v>41935</v>
       </c>
       <c r="O129" t="inlineStr">
@@ -13304,7 +13292,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N130" s="2" t="n">
+      <c r="N130" s="1" t="n">
         <v>41799</v>
       </c>
       <c r="O130" t="inlineStr">
@@ -13402,7 +13390,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N131" s="2" t="n">
+      <c r="N131" s="1" t="n">
         <v>42745</v>
       </c>
       <c r="O131" t="inlineStr">
@@ -13500,7 +13488,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N132" s="2" t="n">
+      <c r="N132" s="1" t="n">
         <v>37869</v>
       </c>
       <c r="O132" t="inlineStr">
@@ -13598,7 +13586,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N133" s="2" t="n">
+      <c r="N133" s="1" t="n">
         <v>37567</v>
       </c>
       <c r="O133" t="inlineStr">
@@ -13696,7 +13684,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N134" s="2" t="n">
+      <c r="N134" s="1" t="n">
         <v>37869</v>
       </c>
       <c r="O134" t="inlineStr">
@@ -13794,7 +13782,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N135" s="2" t="n">
+      <c r="N135" s="1" t="n">
         <v>40361</v>
       </c>
       <c r="O135" t="inlineStr">
@@ -13894,7 +13882,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N136" s="2" t="n">
+      <c r="N136" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O136" t="inlineStr">
@@ -13992,7 +13980,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N137" s="2" t="n">
+      <c r="N137" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="O137" t="inlineStr">

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V137"/>
+  <dimension ref="A1:V138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14019,6 +14022,104 @@
         </is>
       </c>
       <c r="V137" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE NARIÑO</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>San Andrés de Tumaco</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>105337</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SOCIOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>160</v>
+      </c>
+      <c r="J138" t="n">
+        <v>10</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>365619</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>42417</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Sociología, Antropología y estudios culturales</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14028,10 +14025,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A138" t="n">
+        <v>1206</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -14085,7 +14080,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N138" s="2" t="n">
+      <c r="N138" s="1" t="n">
         <v>42417</v>
       </c>
       <c r="O138" t="inlineStr">

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V138"/>
+  <dimension ref="A1:V140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14115,6 +14118,198 @@
         </is>
       </c>
       <c r="V138" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>104932</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>157</v>
+      </c>
+      <c r="J139" t="n">
+        <v>9</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>42276</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>102406</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>FINANZAS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>139</v>
+      </c>
+      <c r="J140" t="n">
+        <v>9</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>41380</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V140"/>
+  <dimension ref="A1:V143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14124,10 +14124,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A139" t="n">
+        <v>1728</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -14179,7 +14177,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N139" s="2" t="n">
+      <c r="N139" s="1" t="n">
         <v>42276</v>
       </c>
       <c r="O139" t="inlineStr">
@@ -14220,10 +14218,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A140" t="n">
+        <v>1728</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -14275,7 +14271,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N140" s="2" t="n">
+      <c r="N140" s="1" t="n">
         <v>41380</v>
       </c>
       <c r="O140" t="inlineStr">
@@ -14310,6 +14306,296 @@
         </is>
       </c>
       <c r="V140" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>5091</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ADMINISTRACION TURÍSTICA Y HOTELERA</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>153</v>
+      </c>
+      <c r="J141" t="n">
+        <v>9</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>5181066</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>43495</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA VISIÓN DE LAS AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>115868</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN TURÍSTICA Y HOTELERA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>158</v>
+      </c>
+      <c r="J142" t="n">
+        <v>9</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL CARIBE - CECAR</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>103376</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN INGLÉS</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>129</v>
+      </c>
+      <c r="J143" t="n">
+        <v>8</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>41809</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Formación para docentes sin asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14312,10 +14309,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A141" t="n">
+        <v>1823</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -14369,7 +14364,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N141" s="2" t="n">
+      <c r="N141" s="1" t="n">
         <v>43495</v>
       </c>
       <c r="O141" t="inlineStr">
@@ -14410,10 +14405,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
+      <c r="A142" t="n">
+        <v>2747</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -14465,7 +14458,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N142" s="2" t="n">
+      <c r="N142" s="1" t="n">
         <v>45483</v>
       </c>
       <c r="O142" t="inlineStr">
@@ -14506,10 +14499,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
+      <c r="A143" t="n">
+        <v>2823</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -14561,7 +14552,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N143" s="2" t="n">
+      <c r="N143" s="1" t="n">
         <v>41809</v>
       </c>
       <c r="O143" t="inlineStr">

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V143"/>
+  <dimension ref="A1:V148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14587,6 +14590,488 @@
         </is>
       </c>
       <c r="V143" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>104932</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>157</v>
+      </c>
+      <c r="J144" t="n">
+        <v>9</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>42276</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>102406</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>FINANZAS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>139</v>
+      </c>
+      <c r="J145" t="n">
+        <v>9</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>41380</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>5091</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>ADMINISTRACION TURÍSTICA Y HOTELERA</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>153</v>
+      </c>
+      <c r="J146" t="n">
+        <v>9</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>5181066</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>43495</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA VISIÓN DE LAS AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>115868</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN TURÍSTICA Y HOTELERA</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>158</v>
+      </c>
+      <c r="J147" t="n">
+        <v>9</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL CARIBE - CECAR</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>103376</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN INGLÉS</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>129</v>
+      </c>
+      <c r="J148" t="n">
+        <v>8</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>41809</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Formación para docentes sin asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14596,10 +14593,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A144" t="n">
+        <v>1728</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -14651,7 +14646,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N144" s="2" t="n">
+      <c r="N144" s="1" t="n">
         <v>42276</v>
       </c>
       <c r="O144" t="inlineStr">
@@ -14692,10 +14687,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A145" t="n">
+        <v>1728</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -14747,7 +14740,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N145" s="2" t="n">
+      <c r="N145" s="1" t="n">
         <v>41380</v>
       </c>
       <c r="O145" t="inlineStr">
@@ -14788,10 +14781,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A146" t="n">
+        <v>1823</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -14845,7 +14836,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N146" s="2" t="n">
+      <c r="N146" s="1" t="n">
         <v>43495</v>
       </c>
       <c r="O146" t="inlineStr">
@@ -14886,10 +14877,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
+      <c r="A147" t="n">
+        <v>2747</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -14941,7 +14930,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N147" s="2" t="n">
+      <c r="N147" s="1" t="n">
         <v>45483</v>
       </c>
       <c r="O147" t="inlineStr">
@@ -14982,10 +14971,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
+      <c r="A148" t="n">
+        <v>2823</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -15037,7 +15024,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N148" s="2" t="n">
+      <c r="N148" s="1" t="n">
         <v>41809</v>
       </c>
       <c r="O148" t="inlineStr">

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V148"/>
+  <dimension ref="A1:V151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15059,6 +15062,296 @@
         </is>
       </c>
       <c r="V148" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>101940</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>157</v>
+      </c>
+      <c r="J149" t="n">
+        <v>8</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>11027700</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>43495</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>107287</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>FILOSOFÍA Y HUMANIDADES</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>124</v>
+      </c>
+      <c r="J150" t="n">
+        <v>8</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>43327</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Filosofía y ética</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>54126</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>FINANZAS Y COMERCIO EXTERIOR</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>154</v>
+      </c>
+      <c r="J151" t="n">
+        <v>9</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>43292</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15068,10 +15065,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A149" t="n">
+        <v>1728</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -15125,7 +15120,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N149" s="2" t="n">
+      <c r="N149" s="1" t="n">
         <v>43495</v>
       </c>
       <c r="O149" t="inlineStr">
@@ -15166,10 +15161,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A150" t="n">
+        <v>1728</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -15221,7 +15214,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N150" s="2" t="n">
+      <c r="N150" s="1" t="n">
         <v>43327</v>
       </c>
       <c r="O150" t="inlineStr">
@@ -15262,10 +15255,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A151" t="n">
+        <v>1728</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -15317,7 +15308,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N151" s="2" t="n">
+      <c r="N151" s="1" t="n">
         <v>43292</v>
       </c>
       <c r="O151" t="inlineStr">

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V151"/>
+  <dimension ref="A1:V152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15343,6 +15346,104 @@
         </is>
       </c>
       <c r="V151" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>4343</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>DISEÑO INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>129</v>
+      </c>
+      <c r="J152" t="n">
+        <v>8</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>15579660</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>44778</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V152"/>
+  <dimension ref="A1:V153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15352,10 +15352,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A152" t="n">
+        <v>1828</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -15409,7 +15407,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N152" s="2" t="n">
+      <c r="N152" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="O152" t="inlineStr">
@@ -15444,6 +15442,104 @@
         </is>
       </c>
       <c r="V152" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INDUSTRIAL DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Socorro</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>101718</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>TURISMO</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>131</v>
+      </c>
+      <c r="J153" t="n">
+        <v>8</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>1997090</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>43490</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Servicios personales</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Viajes, turismo y actividades recreativas</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V153"/>
+  <dimension ref="A1:V161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15448,10 +15448,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A153" t="n">
+        <v>1204</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -15505,7 +15503,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N153" s="2" t="n">
+      <c r="N153" s="1" t="n">
         <v>43490</v>
       </c>
       <c r="O153" t="inlineStr">
@@ -15540,6 +15538,784 @@
         </is>
       </c>
       <c r="V153" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DEL CARIBE- UNIAUTONOMA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>3695</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>INGENIERIA ELECTRONICA Y TELECOMUNICACIONES</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>156</v>
+      </c>
+      <c r="J154" t="n">
+        <v>9</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>6099526</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>35875</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>107743</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>INGENIERIA COMERCIAL.</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>150</v>
+      </c>
+      <c r="J155" t="n">
+        <v>9</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>43557</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Ventas al por mayor y al por menor</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>106441</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN CIENCIAS NATURALES</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>162</v>
+      </c>
+      <c r="J156" t="n">
+        <v>9</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>42991</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>106625</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN CIENCIAS SOCIALES.</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>160</v>
+      </c>
+      <c r="J157" t="n">
+        <v>9</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>43112</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>107394</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EN DISEÑO GRÁFICO</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>144</v>
+      </c>
+      <c r="J158" t="n">
+        <v>8</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>4030000</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>43327</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>4810</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA CENDA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>101390</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACION FISICA, RECREACION Y DEPORTES</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>166</v>
+      </c>
+      <c r="J159" t="n">
+        <v>10</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>3613245</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>40893</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ECCI</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>107938</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>INGENIERIA AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>170</v>
+      </c>
+      <c r="J160" t="n">
+        <v>10</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>4605294</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>43588</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>9129</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CAFAM -UNICAFAM</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>108784</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACION INFANTIL</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>145</v>
+      </c>
+      <c r="J161" t="n">
+        <v>8</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>3950098</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>43850</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Formación para docentes sin asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15544,10 +15541,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
+      <c r="A154" t="n">
+        <v>1804</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -15601,7 +15596,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N154" s="2" t="n">
+      <c r="N154" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O154" t="inlineStr">
@@ -15642,10 +15637,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A155" t="n">
+        <v>1805</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -15697,7 +15690,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N155" s="2" t="n">
+      <c r="N155" s="1" t="n">
         <v>43557</v>
       </c>
       <c r="O155" t="inlineStr">
@@ -15738,10 +15731,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A156" t="n">
+        <v>1805</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -15793,7 +15784,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N156" s="2" t="n">
+      <c r="N156" s="1" t="n">
         <v>42991</v>
       </c>
       <c r="O156" t="inlineStr">
@@ -15834,10 +15825,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A157" t="n">
+        <v>1805</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -15889,7 +15878,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N157" s="2" t="n">
+      <c r="N157" s="1" t="n">
         <v>43112</v>
       </c>
       <c r="O157" t="inlineStr">
@@ -15930,10 +15919,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A158" t="n">
+        <v>2833</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -15987,7 +15974,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N158" s="2" t="n">
+      <c r="N158" s="1" t="n">
         <v>43327</v>
       </c>
       <c r="O158" t="inlineStr">
@@ -16028,10 +16015,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>4810</t>
-        </is>
+      <c r="A159" t="n">
+        <v>4810</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -16085,7 +16070,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N159" s="2" t="n">
+      <c r="N159" s="1" t="n">
         <v>40893</v>
       </c>
       <c r="O159" t="inlineStr">
@@ -16126,10 +16111,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>5802</t>
-        </is>
+      <c r="A160" t="n">
+        <v>5802</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -16183,7 +16166,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N160" s="2" t="n">
+      <c r="N160" s="1" t="n">
         <v>43588</v>
       </c>
       <c r="O160" t="inlineStr">
@@ -16224,10 +16207,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>9129</t>
-        </is>
+      <c r="A161" t="n">
+        <v>9129</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -16281,7 +16262,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N161" s="2" t="n">
+      <c r="N161" s="1" t="n">
         <v>43850</v>
       </c>
       <c r="O161" t="inlineStr">

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V161"/>
+  <dimension ref="A1:V162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16297,6 +16300,104 @@
         </is>
       </c>
       <c r="V161" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DEL CARIBE- UNIAUTONOMA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>90660</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>NEGOCIOS Y FINANZAS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>140</v>
+      </c>
+      <c r="J162" t="n">
+        <v>8</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>3987838</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>40386</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V163"/>
+  <dimension ref="A1:V166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16402,10 +16402,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
+      <c r="A163" t="n">
+        <v>1101</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -16457,7 +16455,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N163" s="2" t="n">
+      <c r="N163" s="1" t="n">
         <v>38205</v>
       </c>
       <c r="O163" t="inlineStr">
@@ -16492,6 +16490,296 @@
         </is>
       </c>
       <c r="V163" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>116650</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>INGENIERIA AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>135</v>
+      </c>
+      <c r="J164" t="n">
+        <v>8</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>4071</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>BACTERIOLOGIA</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>176</v>
+      </c>
+      <c r="J165" t="n">
+        <v>10</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>6506185</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>35875</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Tecnología de diagnóstico y tratamiento médico</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Bacteriología</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INTERNACIONAL DEL TRÓPICO AMERICANO - UNITRÓPICO</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>116114</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>154</v>
+      </c>
+      <c r="J166" t="n">
+        <v>9</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="n">
+        <v>45105</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V166"/>
+  <dimension ref="A1:V167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16496,10 +16496,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A164" t="n">
+        <v>1709</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -16551,7 +16549,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N164" s="2" t="n">
+      <c r="N164" s="1" t="n">
         <v>45274</v>
       </c>
       <c r="O164" t="inlineStr">
@@ -16592,10 +16590,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
+      <c r="A165" t="n">
+        <v>1724</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -16649,7 +16645,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N165" s="2" t="n">
+      <c r="N165" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O165" t="inlineStr">
@@ -16690,10 +16686,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
+      <c r="A166" t="n">
+        <v>2743</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -16745,7 +16739,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N166" s="2" t="n">
+      <c r="N166" s="1" t="n">
         <v>45105</v>
       </c>
       <c r="O166" t="inlineStr">
@@ -16780,6 +16774,104 @@
         </is>
       </c>
       <c r="V166" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA - ITM</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>103928</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN DISEÑO INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>180</v>
+      </c>
+      <c r="J167" t="n">
+        <v>10</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>1449066</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="n">
+        <v>41990</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>
